--- a/static/download/Contractor_Report_4.xlsx
+++ b/static/download/Contractor_Report_4.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Aarham International</t>
+          <t>Aadi Shakti Construction</t>
         </is>
       </c>
     </row>
@@ -641,450 +641,370 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51760</t>
+          <t>59485</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yarpur</t>
+          <t>bhaneri jaat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pipeline laying work</t>
+          <t>oht work</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Yarpur Village Pipeline laying work</t>
+          <t>Bhaneri Jaat Village OHT work</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>44851</v>
+        <v>45196</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1198373</v>
+        <v>499500</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>234648</v>
       </c>
       <c r="I13" t="n">
-        <v>1198373</v>
+        <v>264852</v>
       </c>
       <c r="J13" t="n">
-        <v>215707</v>
+        <v>47673</v>
       </c>
       <c r="K13" t="n">
-        <v>1414080</v>
+        <v>312525</v>
       </c>
       <c r="L13" t="n">
-        <v>23967.46</v>
+        <v>2649</v>
       </c>
       <c r="M13" t="n">
-        <v>59918.65</v>
+        <v>13243</v>
       </c>
       <c r="N13" t="n">
-        <v>59918.65</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>119837</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>215707</v>
+        <v>47673</v>
       </c>
       <c r="Q13" t="n">
-        <v>215632</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>719099</v>
+        <v>248960</v>
       </c>
       <c r="S13" t="n">
-        <v>220500</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>220500</v>
+        <v>248960</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>08-08-2022 NEFT/AXISP00310461061/RIUP22/470/AARHAM INTERNATI 220500.00</t>
+          <t>10-10-2023 NEFT/AXISP00432944784/RIUP23/2526/AADI SHAKTI CONSTR/PUNB0388500 248960.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51760</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yarpur</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>pipeline laying work</t>
-        </is>
-      </c>
+          <t>59485</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Yarpur Village Pipeline laying work</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>45188</v>
-      </c>
+          <t>GST Release Note</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>105083</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>105083</v>
-      </c>
-      <c r="J14" t="n">
-        <v>18915</v>
-      </c>
-      <c r="K14" t="n">
-        <v>123998</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1050.83</v>
-      </c>
-      <c r="M14" t="n">
-        <v>5254</v>
-      </c>
-      <c r="N14" t="n">
-        <v>10508</v>
-      </c>
-      <c r="O14" t="n">
-        <v>10508</v>
-      </c>
-      <c r="P14" t="n">
-        <v>18915</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>11709</v>
-      </c>
+        <v>47673</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>66053</v>
-      </c>
-      <c r="S14" t="n">
-        <v>8600</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
+        <v>47673</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>8600</v>
+        <v>126000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>20-10-2022 NEFT/AXISP00330319204/RIUP22/1075/AARHAM INTERNAT 8600.00</t>
+          <t>29-11-2023 NEFT/AXISP00447355223/RIUP23/3407/AADI SHAKTI CONSTR/PUNB0388500 126000.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51760</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>yarpur</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>pipeline laying work</t>
-        </is>
-      </c>
+          <t>59485</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Yarpur Village Pipeline laying work</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>45188</v>
-      </c>
+          <t>GST Release Note</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>755469</v>
-      </c>
-      <c r="H15" t="n">
-        <v>89652</v>
-      </c>
-      <c r="I15" t="n">
-        <v>665817</v>
-      </c>
-      <c r="J15" t="n">
-        <v>119847</v>
-      </c>
-      <c r="K15" t="n">
-        <v>785664</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6658</v>
-      </c>
-      <c r="M15" t="n">
-        <v>33291</v>
-      </c>
-      <c r="N15" t="n">
-        <v>66582</v>
-      </c>
-      <c r="O15" t="n">
-        <v>66582</v>
-      </c>
-      <c r="P15" t="n">
-        <v>119847</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>8354</v>
-      </c>
+        <v>63257.13</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>484350</v>
-      </c>
-      <c r="S15" t="n">
-        <v>215707</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
+        <v>63257.13</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>215707</v>
+        <v>105200</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>22-11-2022 NEFT/AXISP00339527010/RIUP22/1315/AARHAM INTERNAT 215707.00</t>
+          <t>24-04-2024 NEFT/AXISP00493457025/RIUP24/0184/AADI SHAKTI CONSTR/PUNB0388500 105200.00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
-      <c r="V16" s="3" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>59485</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GST Release Note</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>69428.52</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>69428.52</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>69429</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>06-12-2023 NEFT/AXISP00450230173/RIUP23/3623/AADI SHAKTI CONSTR/PUNB0388500 69429.00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>52429</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>bhogimazra</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>pipeline laying work</t>
-        </is>
-      </c>
+          <t>59485</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bhogimazra Village Pipeline laying work</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>44841</v>
-      </c>
+          <t>GST Release Note</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>209791</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>209791</v>
-      </c>
-      <c r="J17" t="n">
-        <v>37762</v>
-      </c>
-      <c r="K17" t="n">
-        <v>247553</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4195.82</v>
-      </c>
-      <c r="M17" t="n">
-        <v>10490</v>
-      </c>
-      <c r="N17" t="n">
-        <v>10490</v>
-      </c>
-      <c r="O17" t="n">
-        <v>20979</v>
-      </c>
-      <c r="P17" t="n">
-        <v>37762</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>17255</v>
-      </c>
+        <v>105199.56</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>146381.18</v>
-      </c>
-      <c r="S17" t="n">
-        <v>150000</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
+        <v>105199.56</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>147000</v>
+        <v>148500</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>20-10-2022 NEFT/AXISP00330252336/RIUP22/1059/AARHAM INTERNAT 147000.00</t>
+          <t>25-01-2024 NEFT/AXISP00464983349/RIUP23/4470/AADI SHAKTI CONSTR/PUNB0388500  148500.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>59485</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bhogimazra</t>
+          <t>bhaneri jaat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pipeline laying work</t>
+          <t>oht work</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bhogimazra Village Pipeline laying work</t>
+          <t>Bhaneri Jaat Village OHT work</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44932</v>
+        <v>45229</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>249850</v>
+        <v>832500</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>446786</v>
       </c>
       <c r="I18" t="n">
-        <v>249850</v>
+        <v>385714</v>
       </c>
       <c r="J18" t="n">
-        <v>44973</v>
+        <v>69428.52</v>
       </c>
       <c r="K18" t="n">
-        <v>294823</v>
+        <v>455142.52</v>
       </c>
       <c r="L18" t="n">
-        <v>4997</v>
+        <v>3857.14</v>
       </c>
       <c r="M18" t="n">
-        <v>12493</v>
+        <v>19285.7</v>
       </c>
       <c r="N18" t="n">
-        <v>24985</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>24985</v>
+        <v>38571.4</v>
       </c>
       <c r="P18" t="n">
-        <v>44973</v>
+        <v>69428.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>63367</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>119023</v>
+        <v>324000</v>
       </c>
       <c r="S18" t="n">
-        <v>119023</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>119023</v>
+        <v>47673</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>18-01-2023 NEFT/AXISP00355694664/RIUP22/1829/AARHAM INTERNAT 119023.00</t>
+          <t>03-11-2023 NEFT/AXISP00440155778/RIUP23/3003/AADI SHAKTI CONSTR/PUNB0388500 47673.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>59485</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bhogimazra</t>
+          <t>bhaneri jaat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pipeline laying work</t>
+          <t>oht work</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bhogimazra Village Pipeline laying work</t>
+          <t>Bhaneri Jaat Village OHT work</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>44932</v>
+        <v>45329</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1092,420 +1012,337 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>62098</v>
+        <v>999000</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>414558</v>
       </c>
       <c r="I19" t="n">
-        <v>62098</v>
+        <v>584442</v>
       </c>
       <c r="J19" t="n">
-        <v>11178</v>
+        <v>105199.56</v>
       </c>
       <c r="K19" t="n">
-        <v>73276</v>
+        <v>689641.5600000001</v>
       </c>
       <c r="L19" t="n">
-        <v>1241.96</v>
+        <v>5844.42</v>
       </c>
       <c r="M19" t="n">
-        <v>3105</v>
+        <v>29222.1</v>
       </c>
       <c r="N19" t="n">
-        <v>6210</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6210</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>11178</v>
+        <v>105199.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>14615</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>30716.04</v>
+        <v>549375</v>
       </c>
       <c r="S19" t="n">
-        <v>44973</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>44973</v>
+        <v>198000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>24-02-2023 NEFT/AXISP00365286192/RIUP22/2278/AARHAM INTERNAT 44973.00</t>
+          <t>09-11-2023 NEFT/AXISP00442541879/RIUP23/3167/AADI SHAKTI CONSTR/PUNB0388500 198000.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>59485</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bhogimazra</t>
+          <t>bhaneri jaat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pipeline laying work</t>
+          <t>oht work</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bhogimazra Village Pipeline laying work</t>
+          <t>Bhaneri Jaat Village OHT  work</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45174</v>
+        <v>45478</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>301032</v>
+        <v>765900</v>
       </c>
       <c r="H20" t="n">
-        <v>47687</v>
+        <v>414471.52</v>
       </c>
       <c r="I20" t="n">
-        <v>253345</v>
+        <v>351428.48</v>
       </c>
       <c r="J20" t="n">
-        <v>45602</v>
+        <v>63257.13</v>
       </c>
       <c r="K20" t="n">
-        <v>298947</v>
+        <v>414685.61</v>
       </c>
       <c r="L20" t="n">
-        <v>5066.9</v>
+        <v>3514.28</v>
       </c>
       <c r="M20" t="n">
-        <v>12667</v>
+        <v>17571.42</v>
       </c>
       <c r="N20" t="n">
-        <v>25335</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>25335</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>45602</v>
+        <v>63257.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>5278</v>
+        <v>166500</v>
       </c>
       <c r="R20" t="n">
-        <v>179663.1</v>
+        <v>163843</v>
       </c>
       <c r="S20" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>98000</v>
+        <v>400876</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>16-06-2023 NEFT/AXISP00399073691/RIUP23/693/AARHAM INTERNATI 98000.00</t>
+          <t>20-02-2024 NEFT/AXISP00464478563/RIUP23/4675/AADI SHAKTI CONSTR/PUNB0388500  400876.00</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr"/>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr"/>
-      <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="3" t="inlineStr"/>
-      <c r="V21" s="3" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>59485</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>bhaneri jaat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>oht work</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bhaneri Jaat Village OHT work</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>45723</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>233100</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>233100</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41958</v>
+      </c>
+      <c r="K21" t="n">
+        <v>275058</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2331</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11655</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>41958</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>233100</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>247500</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>31-07-2024 NEFT/AXISP00522988547/RIUP24/1308/AADI SHAKTI CONSTR/PUNB0388500 247500.00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>53817</t>
+          <t>59485</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bibipur hatiya</t>
+          <t>bhaneri jaat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pipeline laying work</t>
+          <t>oht work</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bibipur Hatiya Village Pipeline laying work</t>
+          <t>Bhaneri Jaat Village OHT work</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>44910</v>
+        <v>45600</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>819165</v>
+        <v>38571</v>
       </c>
       <c r="H22" t="n">
-        <v>63049</v>
-      </c>
-      <c r="I22" t="n">
-        <v>756116</v>
-      </c>
-      <c r="J22" t="n">
-        <v>136101</v>
-      </c>
-      <c r="K22" t="n">
-        <v>892217</v>
-      </c>
-      <c r="L22" t="n">
-        <v>15122</v>
-      </c>
-      <c r="M22" t="n">
-        <v>37806</v>
-      </c>
-      <c r="N22" t="n">
-        <v>75612</v>
-      </c>
-      <c r="O22" t="n">
-        <v>75612</v>
-      </c>
-      <c r="P22" t="n">
-        <v>136101</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>99041</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>452923</v>
+        <v>38571</v>
       </c>
       <c r="S22" t="n">
-        <v>452923</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>452923</v>
+        <v>99000</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>03-01-2023 NEFT/AXISP00351384277/RIUP22/1744/AARHAM INTERNAT 452923.00</t>
+          <t>20-08-2024 NEFT/AXISP00530112320/RIUP24/1505/AADI SHAKTI CONSTR/PUNB0388500 99000.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>53817</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>bibipur hatiya</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>pipeline laying work</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Bibipur Hatiya Village Pipeline laying work</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>44953</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>351667</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>351667</v>
-      </c>
-      <c r="J23" t="n">
-        <v>63300</v>
-      </c>
-      <c r="K23" t="n">
-        <v>414967</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7033</v>
-      </c>
-      <c r="M23" t="n">
-        <v>17583</v>
-      </c>
-      <c r="N23" t="n">
-        <v>35167</v>
-      </c>
-      <c r="O23" t="n">
-        <v>35167</v>
-      </c>
-      <c r="P23" t="n">
-        <v>63300</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>71654</v>
-      </c>
-      <c r="R23" t="n">
-        <v>185063</v>
-      </c>
+          <t>59485</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>185036</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>185036</v>
+        <v>198000</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>31-01-2023 NEFT/AXISP00358425205/RIUP22/2043/AARHAM INTERNAT 185063.00</t>
+          <t>14-11-2024 NEFT/AXISP00569462153/RIUP24/2472/AADI SHAKTI CONSTR/PUNB0388500 198000.00</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>53817</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>bibipur hatiya</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>pipeline laying work</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Bibipur Hatiya Village Pipeline laying work</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>45131</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>65747.32000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>65747.32000000001</v>
-      </c>
-      <c r="J24" t="n">
-        <v>11835</v>
-      </c>
-      <c r="K24" t="n">
-        <v>77582</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1315</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3287</v>
-      </c>
-      <c r="N24" t="n">
-        <v>6575</v>
-      </c>
-      <c r="O24" t="n">
-        <v>6575</v>
-      </c>
-      <c r="P24" t="n">
-        <v>11835</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1224</v>
-      </c>
-      <c r="R24" t="n">
-        <v>46771</v>
-      </c>
-      <c r="S24" t="n">
-        <v>100000</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>98000</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>13-04-2023 13-04-2023 NEFT/AXISP00381797400/SPUP23/0122/AARHAM INTERNAT 98000.00</t>
-        </is>
-      </c>
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr"/>
+      <c r="V24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>53817</t>
+          <t>59486</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bibipur hatiya</t>
+          <t>kasampur</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pipeline laying work</t>
+          <t>50kl 12m staging oht work</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bibipur Hatiya Village Pipeline laying work</t>
+          <t>Kasampur Village 50KL 12m Staging  OHT work</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45131</v>
+        <v>45229</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1513,25 +1350,25 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>453007.5</v>
+        <v>204750</v>
       </c>
       <c r="H25" t="n">
-        <v>66762</v>
+        <v>100791</v>
       </c>
       <c r="I25" t="n">
-        <v>386245.5</v>
+        <v>103959</v>
       </c>
       <c r="J25" t="n">
-        <v>69524</v>
+        <v>18713</v>
       </c>
       <c r="K25" t="n">
-        <v>455770</v>
+        <v>122672</v>
       </c>
       <c r="L25" t="n">
-        <v>7725</v>
+        <v>1040</v>
       </c>
       <c r="M25" t="n">
-        <v>19312</v>
+        <v>5198</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -1540,262 +1377,271 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>69524</v>
+        <v>18713</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>359209</v>
+        <v>97721</v>
       </c>
       <c r="S25" t="n">
-        <v>78400</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>78400</v>
+        <v>97721</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>16-06-2023 NEFT/AXISP00399073687/RIUP23/694/AARHAM INTERNATI 78400.00</t>
+          <t>09-11-2023 NEFT/AXISP00442506532/RIUP23/3143/AADI SHAKTI CONSTR/PUNB0388500 97721.00</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="inlineStr"/>
-      <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="3" t="inlineStr"/>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="3" t="inlineStr"/>
-      <c r="T26" s="3" t="inlineStr"/>
-      <c r="U26" s="3" t="inlineStr"/>
-      <c r="V26" s="3" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>59486</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GST Release Note</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>52151</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="n">
+        <v>52151</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="n">
+        <v>99000</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>19-08-2024 NEFT/AXISP00529670925/RIUP24/1489/AADI SHAKTI CONSTR/PUNB0388500 99000.00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>55128</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>hasanpur</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>pipe laying work</t>
-        </is>
-      </c>
+          <t>59486</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">HASANPUR Village Pipe laying work </t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>44985</v>
-      </c>
+          <t>GST Release Note</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>572623.25</v>
-      </c>
-      <c r="H27" t="n">
-        <v>40532</v>
-      </c>
-      <c r="I27" t="n">
-        <v>532091.25</v>
-      </c>
-      <c r="J27" t="n">
-        <v>95776</v>
-      </c>
-      <c r="K27" t="n">
-        <v>627867</v>
-      </c>
-      <c r="L27" t="n">
-        <v>5320.91</v>
-      </c>
-      <c r="M27" t="n">
-        <v>26604.56</v>
-      </c>
-      <c r="N27" t="n">
-        <v>53209.13</v>
-      </c>
-      <c r="O27" t="n">
-        <v>53209.13</v>
-      </c>
-      <c r="P27" t="n">
-        <v>95776</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>38678</v>
-      </c>
+        <v>18713</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>355069</v>
-      </c>
-      <c r="S27" t="n">
-        <v>200000</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
+        <v>18713</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
-        <v>196000</v>
+        <v>18713</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>08-03-2023 NEFT/AXISP00369766204/RIUP22/2502/AARHAM INTERNAT 196000.00</t>
+          <t>06-12-2023 NEFT/AXISP00450230172/RIUP23/3624/AADI SHAKTI CONSTR/PUNB0388500 18713.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>59486</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>hasanpur</t>
+          <t>kasampur</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>pipe laying work</t>
+          <t>50kl 12m staging oht work</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">HASANPUR Village Pipe laying work </t>
+          <t>Kasampur Village 50KL 12m Staging  OHT work</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>45055</v>
+        <v>45478</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>407456</v>
+        <v>341250</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>51525</v>
       </c>
       <c r="I28" t="n">
-        <v>407456</v>
+        <v>289725</v>
       </c>
       <c r="J28" t="n">
-        <v>73342</v>
+        <v>52151</v>
       </c>
       <c r="K28" t="n">
-        <v>480798</v>
+        <v>341876</v>
       </c>
       <c r="L28" t="n">
-        <v>4074.56</v>
+        <v>2897</v>
       </c>
       <c r="M28" t="n">
-        <v>20372.8</v>
+        <v>14486</v>
       </c>
       <c r="N28" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>40745.6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>73342</v>
+        <v>52151</v>
       </c>
       <c r="Q28" t="n">
-        <v>97239</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>204279</v>
+        <v>272342</v>
       </c>
       <c r="S28" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>98000</v>
+        <v>250000</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>21-03-2023 NEFT/AXISP00373201702/RIUP22/2685/AARHAM INTERNAT 98000.00</t>
+          <t>31-07-2024 NEFT/AXISP00522988539/RIUP24/1118/AADI SHAKTI CONSTR/PUNB0388500 250000.00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>59486</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hansanpur</t>
+          <t>kasampur</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>debit note work</t>
+          <t>50kl 12m staging oht work</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Hansanpur Village DEBIT NOTE work</t>
+          <t>Kasampur Village 50KL 12m Staging  OHT work</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>45670</v>
+        <v>45723</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>85754</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+        <v>682500</v>
+      </c>
+      <c r="H29" t="n">
+        <v>310069</v>
+      </c>
+      <c r="I29" t="n">
+        <v>372431</v>
+      </c>
+      <c r="J29" t="n">
+        <v>67038</v>
+      </c>
+      <c r="K29" t="n">
+        <v>439469</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3724</v>
+      </c>
+      <c r="M29" t="n">
+        <v>18622</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>67038</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
       <c r="R29" t="n">
-        <v>85754</v>
+        <v>350085</v>
       </c>
       <c r="S29" t="n">
-        <v>95776</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>95776</v>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>20-05-2023 NEFT/AXISP00391552051/RIUP23/303/AARHAM INTERNATI ₹ 95,776.00</t>
-        </is>
       </c>
     </row>
     <row r="30">
@@ -1825,681 +1671,563 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>57798</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ahmadpur</t>
+          <t>bhikki mazra</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>pipeline laying work</t>
+          <t>50kl 14m staging oht work</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ahmadpur  Village Pipeline laying work</t>
+          <t>Bhikki Mazra Village 50KL 14m Staging  OHT work</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>45083</v>
+        <v>45229</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>646976</v>
+        <v>380250</v>
       </c>
       <c r="H31" t="n">
-        <v>18014</v>
+        <v>170291</v>
       </c>
       <c r="I31" t="n">
-        <v>628962</v>
+        <v>209959</v>
       </c>
       <c r="J31" t="n">
-        <v>113213</v>
+        <v>37793</v>
       </c>
       <c r="K31" t="n">
-        <v>742175</v>
+        <v>247752</v>
       </c>
       <c r="L31" t="n">
-        <v>12579.24</v>
+        <v>2100</v>
       </c>
       <c r="M31" t="n">
-        <v>31448</v>
+        <v>10498</v>
       </c>
       <c r="N31" t="n">
-        <v>62896</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>62896</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>113213</v>
+        <v>37793</v>
       </c>
       <c r="Q31" t="n">
-        <v>3450</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>455693</v>
+        <v>197361</v>
       </c>
       <c r="S31" t="n">
-        <v>455693</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>455693</v>
+        <v>197361</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>16-06-2023 NEFT/AXISP00399009125/RIUP23/661/AARHAM INTERNATI 455693.00</t>
+          <t>09-11-2023 NEFT/AXISP00442506533/RIUP23/3147/AADI SHAKTI CONSTR/PUNB0388500 197361.00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>57798</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ahmadpur</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>pipeline laying work</t>
-        </is>
-      </c>
+          <t>59487</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ahmadpur  Village Pipeline laying work</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>45230</v>
-      </c>
+          <t>GST Release Note</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>398973</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>398973</v>
-      </c>
-      <c r="J32" t="n">
-        <v>71815</v>
-      </c>
-      <c r="K32" t="n">
-        <v>470788</v>
-      </c>
-      <c r="L32" t="n">
-        <v>7979.46</v>
-      </c>
-      <c r="M32" t="n">
-        <v>19949</v>
-      </c>
-      <c r="N32" t="n">
-        <v>39897</v>
-      </c>
-      <c r="O32" t="n">
-        <v>39897</v>
-      </c>
-      <c r="P32" t="n">
-        <v>71815</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>96271</v>
-      </c>
+        <v>37793</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
-        <v>194980</v>
-      </c>
-      <c r="S32" t="n">
-        <v>113213</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
+        <v>37793</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="n">
-        <v>113213</v>
+        <v>37793</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>31-07-2023 NEFT/AXISP00410478614/RIUP23/1272/AARHAM INTERNAT ₹ 1,13,213.00</t>
+          <t>06-12-2023 NEFT/AXISP00450230174/RIUP23/3625/AADI SHAKTI CONSTR/PUNB0388500 37793.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>57798</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ahmadpur</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>pipeline laying work</t>
-        </is>
-      </c>
+          <t>59487</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ahmadpur  Village Pipeline laying work</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>45311</v>
-      </c>
+          <t>GST Release Note</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>62610</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>62610</v>
-      </c>
-      <c r="J33" t="n">
-        <v>11270</v>
-      </c>
-      <c r="K33" t="n">
-        <v>73880</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1252.2</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3131</v>
-      </c>
-      <c r="N33" t="n">
-        <v>6261</v>
-      </c>
-      <c r="O33" t="n">
-        <v>6261</v>
-      </c>
-      <c r="P33" t="n">
-        <v>11270</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1765</v>
-      </c>
+        <v>7984</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>43940</v>
-      </c>
-      <c r="S33" t="n">
-        <v>42920</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
+        <v>7984</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="n">
-        <v>42920</v>
+        <v>495000</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>06-03-2024 NEFT/AXISP00477669910/RIUP23/4644/AARHAM INTERNATION/SBIN0011556 42920.00</t>
+          <t>30-10-2024 NEFT/AXISP00561389904/RIUP24/2360/AADI SHAKTI CONSTR/PUNB0388500 495000.00</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr"/>
-      <c r="B34" s="3" t="inlineStr"/>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
-      <c r="O34" s="3" t="inlineStr"/>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="inlineStr"/>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="3" t="inlineStr"/>
-      <c r="V34" s="3" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>59487</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>GST Release Note</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>135584</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>135584</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>59739</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>nai nagla sakauti</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>pipeline laying work</t>
-        </is>
-      </c>
+          <t>59487</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Nai Nagla Sakauti  Village Pipeline laying work</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>44895</v>
-      </c>
+          <t>GST Release Note</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>466158</v>
-      </c>
-      <c r="H35" t="n">
-        <v>36028</v>
-      </c>
-      <c r="I35" t="n">
-        <v>430130</v>
-      </c>
-      <c r="J35" t="n">
-        <v>77423</v>
-      </c>
-      <c r="K35" t="n">
-        <v>507553</v>
-      </c>
-      <c r="L35" t="n">
-        <v>8602.6</v>
-      </c>
-      <c r="M35" t="n">
-        <v>21507</v>
-      </c>
-      <c r="N35" t="n">
-        <v>43013</v>
-      </c>
-      <c r="O35" t="n">
-        <v>43013</v>
-      </c>
-      <c r="P35" t="n">
-        <v>77423</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>175368</v>
-      </c>
+        <v>99512</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
-        <v>138626</v>
-      </c>
-      <c r="S35" t="n">
-        <v>100000</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
+        <v>99512</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="n">
-        <v>98000</v>
+        <v>99512</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>13-10-2023 NEFT/AXISP00434019644/RIUP23/2633/AARHAM INTERNATION 98000.00</t>
+          <t>16-05-2024 NEFT/AXISP00500630402/RIUP24/0351/AADI SHAKTI CONSTR/PUNB0388500 99512.00</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr"/>
-      <c r="B36" s="3" t="inlineStr"/>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
-      <c r="O36" s="3" t="inlineStr"/>
-      <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
-      <c r="T36" s="3" t="inlineStr"/>
-      <c r="U36" s="3" t="inlineStr"/>
-      <c r="V36" s="3" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>59487</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>bhikki mazra</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>50kl 14m staging oht work</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bhikki Mazra Village 50KL 14m Staging  OHT work</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>45369</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>633750</v>
+      </c>
+      <c r="H36" t="n">
+        <v>80906</v>
+      </c>
+      <c r="I36" t="n">
+        <v>552844</v>
+      </c>
+      <c r="J36" t="n">
+        <v>99512</v>
+      </c>
+      <c r="K36" t="n">
+        <v>652356</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5528</v>
+      </c>
+      <c r="M36" t="n">
+        <v>27642</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>99512</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>519674</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>519674</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>22-03-2024 NEFT/AXISP00483290486/RIUP23/5233/AADI SHAKTI CONSTR/PUNB0388500 519674.00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>59740</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>kadarpur</t>
+          <t>bhikki mazra</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pipe line &amp; fhtc work</t>
+          <t>50kl 14m staging oht work</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KADARPUR VILLAGE Pipe Line &amp; FHTC Work</t>
+          <t>Bhikki Mazra Village 50KL 14m Staging  OHT work</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>45291</v>
+        <v>45517</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>356029</v>
+        <v>253500</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>209143</v>
       </c>
       <c r="I37" t="n">
-        <v>356029</v>
+        <v>44357</v>
       </c>
       <c r="J37" t="n">
-        <v>64085</v>
+        <v>7984</v>
       </c>
       <c r="K37" t="n">
-        <v>420114</v>
+        <v>52341</v>
       </c>
       <c r="L37" t="n">
-        <v>7120.58</v>
+        <v>444</v>
       </c>
       <c r="M37" t="n">
-        <v>17801</v>
+        <v>2218</v>
       </c>
       <c r="N37" t="n">
-        <v>35603</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>35603</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>64085</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>40934</v>
-      </c>
+        <v>7984</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
-        <v>218967</v>
+        <v>41695</v>
       </c>
       <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>99000</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>20-08-2024 NEFT/AXISP00530112321/RIUP24/1506/AADI SHAKTI CONSTR/PUNB0388500 99000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>59487</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>bhikki mazra</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>50kl 14m staging oht work</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Bhikki Mazra Village 50KL 14m Staging  OHT work</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>45587</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>912600</v>
+      </c>
+      <c r="H38" t="n">
+        <v>159353</v>
+      </c>
+      <c r="I38" t="n">
+        <v>753247</v>
+      </c>
+      <c r="J38" t="n">
+        <v>135584</v>
+      </c>
+      <c r="K38" t="n">
+        <v>888831</v>
+      </c>
+      <c r="L38" t="n">
+        <v>7532</v>
+      </c>
+      <c r="M38" t="n">
+        <v>37662</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>135584</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>708053</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
         <v>200000</v>
       </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>196000</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>23-10-2023 NEFT/AXISP00436449476/RIUP23/2823/AARHAM INTERNATION 196000.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr"/>
-      <c r="B38" s="3" t="inlineStr"/>
-      <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="3" t="inlineStr"/>
-      <c r="N38" s="3" t="inlineStr"/>
-      <c r="O38" s="3" t="inlineStr"/>
-      <c r="P38" s="3" t="inlineStr"/>
-      <c r="Q38" s="3" t="inlineStr"/>
-      <c r="R38" s="3" t="inlineStr"/>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="3" t="inlineStr"/>
-      <c r="V38" s="3" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>21-06-2025 NEFT/AXISP00681347820/RIUP25/0513/AADI SHAKTI CONSTR/PUNB0388500 200000.00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>janipur</t>
+          <t>bhikki mazra</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pipeline work</t>
+          <t>50kl 14m staging oht work</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Janipur village Pipeline work</t>
+          <t>Bhikki Mazra Village 50KL 14m Staging  OHT work</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>45369</v>
+        <v>45723</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>641752</v>
+        <v>354900</v>
+      </c>
+      <c r="H39" t="n">
+        <v>15260</v>
       </c>
       <c r="I39" t="n">
-        <v>641752</v>
+        <v>339640</v>
       </c>
       <c r="J39" t="n">
-        <v>115515</v>
+        <v>61135</v>
       </c>
       <c r="K39" t="n">
-        <v>757267</v>
+        <v>400775</v>
       </c>
       <c r="L39" t="n">
-        <v>12835.04</v>
+        <v>3396</v>
       </c>
       <c r="M39" t="n">
-        <v>32088</v>
+        <v>16982</v>
       </c>
       <c r="N39" t="n">
-        <v>64175</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>64175</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>115515</v>
+        <v>61135</v>
       </c>
       <c r="Q39" t="n">
-        <v>84523</v>
+        <v>126750</v>
       </c>
       <c r="R39" t="n">
-        <v>383956</v>
+        <v>192512</v>
       </c>
       <c r="S39" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>196000</v>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>14-05-2024 NEFT/AXISP00499817094/RIUP24/0503/AARHAM INTERNATION/SBIN0011556 196000.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>62902</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>janipur</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>pipeline work</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Janipur village Pipeline work</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>45411</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>115515</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>115515</v>
-      </c>
-      <c r="S40" t="n">
-        <v>274400</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>274400</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>03-08-2024 NEFT/AXISP00524511281/RIUP24/1351/AARHAM INTERNATION/SBIN0011556 274400.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>62902</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>janipur</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>pipeline work</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Janipur village Pipeline work</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>45630</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>50624</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>50624</v>
-      </c>
-      <c r="J41" t="n">
-        <v>9112</v>
-      </c>
-      <c r="K41" t="n">
-        <v>59736</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1012.48</v>
-      </c>
-      <c r="M41" t="n">
-        <v>2531</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5062</v>
-      </c>
-      <c r="O41" t="n">
-        <v>5062</v>
-      </c>
-      <c r="P41" t="n">
-        <v>9112</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>36957</v>
-      </c>
-      <c r="S41" t="n">
-        <v>100000</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>98000</v>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>18-09-2024 NEFT/AXISP00541733386/RIUP24/1830/AARHAM INTERNATION/SBIN0011556 98000.00</t>
-        </is>
       </c>
     </row>
   </sheetData>
